--- a/422-contenu-fhir---mise-à-jour-du-séjour/ig/StructureDefinition-tddui-careplan-projet-personnalise.xlsx
+++ b/422-contenu-fhir---mise-à-jour-du-séjour/ig/StructureDefinition-tddui-careplan-projet-personnalise.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-29T15:49:35+00:00</t>
+    <t>2026-01-30T11:01:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/422-contenu-fhir---mise-à-jour-du-séjour/ig/StructureDefinition-tddui-careplan-projet-personnalise.xlsx
+++ b/422-contenu-fhir---mise-à-jour-du-séjour/ig/StructureDefinition-tddui-careplan-projet-personnalise.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-30T11:01:37+00:00</t>
+    <t>2026-01-30T14:32:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/422-contenu-fhir---mise-à-jour-du-séjour/ig/StructureDefinition-tddui-careplan-projet-personnalise.xlsx
+++ b/422-contenu-fhir---mise-à-jour-du-séjour/ig/StructureDefinition-tddui-careplan-projet-personnalise.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-30T14:32:15+00:00</t>
+    <t>2026-02-09T09:12:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -111,7 +111,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/StructureDefinition/CarePlan|4.0.1</t>
+    <t>http://hl7.org/fhir/StructureDefinition/CarePlan</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -627,11 +627,11 @@
     <t>entrantProjetPerso</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-attachment|2.2.0-ballot}
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-attachment}
 </t>
   </si>
   <si>
-    <t>Pièce jointe</t>
+    <t>TDDUI Attachment</t>
   </si>
   <si>
     <t>Extension permettant de véhiculer des pièces jointes que ce soit pour l'évaluation, l'évènement ou le projet personnalisé. L'extension référence le profil PDSm_SimplifiedPublish.</t>
@@ -1005,11 +1005,11 @@
     <t>auteurStatut</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-status-author|2.2.0-ballot}
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-status-author}
 </t>
   </si>
   <si>
-    <t>TDDUI Auteur statut</t>
+    <t>TDDUI Status Author</t>
   </si>
   <si>
     <t>Extension permettant de représenter la profession du professionnel.</t>
@@ -1066,7 +1066,7 @@
     <t>Used for filtering what plan(s) are retrieved and displayed to different types of users.</t>
   </si>
   <si>
-    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-j367-type-projet-personnalise-ms|20250422120000</t>
+    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-j367-type-projet-personnalise-ms</t>
   </si>
   <si>
     <t>typeProjetPersonnalise</t>
@@ -1112,7 +1112,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-patient|2.2.0-ballot|https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-patient-ins|2.2.0-ballot)
+    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-patient|https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-patient-ins)
 </t>
   </si>
   <si>
@@ -1411,11 +1411,11 @@
     <t>2</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-discriminator|2.2.0-ballot}
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-discriminator}
 </t>
   </si>
   <si>
-    <t>TDDUI Discriminator Extension</t>
+    <t>TDDUI Discriminator</t>
   </si>
   <si>
     <t>Extension pour discriminer les éléments CarePlan.supportingInfo et Goal.note.</t>
@@ -1504,7 +1504,7 @@
     <t>accordUsager</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-consent-accord|2.2.0-ballot)
+    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-consent-accord)
 </t>
   </si>
   <si>
@@ -1570,13 +1570,13 @@
   <si>
     <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
   &lt;coding&gt;
-    &lt;system value="https://interop.esante.gouv.fr/ig/fhir/tddui/CodeSystem/tddui-discriminator-cs"/&gt;
+    &lt;system value="https://interop.esante.gouv.fr/ig/fhir/tddui/CodeSystem/tddui-discriminator"/&gt;
     &lt;code value="accordUsager"/&gt;
   &lt;/coding&gt;
 &lt;/valueCodeableConcept&gt;</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/fhir/tddui/ValueSet/tddui-care-plan-supportingInfo-vs|2.2.0-ballot</t>
+    <t>https://interop.esante.gouv.fr/ig/fhir/tddui/ValueSet/tddui-care-plan-supporting-info</t>
   </si>
   <si>
     <t>Extension.value[x]</t>
@@ -1629,7 +1629,7 @@
   <si>
     <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
   &lt;coding&gt;
-    &lt;system value="https://interop.esante.gouv.fr/ig/fhir/tddui/CodeSystem/tddui-discriminator-cs"/&gt;
+    &lt;system value="https://interop.esante.gouv.fr/ig/fhir/tddui/CodeSystem/tddui-discriminator"/&gt;
     &lt;code value="accordStructure"/&gt;
   &lt;/coding&gt;
 &lt;/valueCodeableConcept&gt;</t>
@@ -2522,7 +2522,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="136.375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="77.6875" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="66.40234375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="86.6484375" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>

--- a/422-contenu-fhir---mise-à-jour-du-séjour/ig/StructureDefinition-tddui-careplan-projet-personnalise.xlsx
+++ b/422-contenu-fhir---mise-à-jour-du-séjour/ig/StructureDefinition-tddui-careplan-projet-personnalise.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-09T09:12:46+00:00</t>
+    <t>2026-02-10T10:23:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/422-contenu-fhir---mise-à-jour-du-séjour/ig/StructureDefinition-tddui-careplan-projet-personnalise.xlsx
+++ b/422-contenu-fhir---mise-à-jour-du-séjour/ig/StructureDefinition-tddui-careplan-projet-personnalise.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-10T10:23:53+00:00</t>
+    <t>2026-02-11T15:25:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/422-contenu-fhir---mise-à-jour-du-séjour/ig/StructureDefinition-tddui-careplan-projet-personnalise.xlsx
+++ b/422-contenu-fhir---mise-à-jour-du-séjour/ig/StructureDefinition-tddui-careplan-projet-personnalise.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-11T15:25:25+00:00</t>
+    <t>2026-02-16T10:05:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/422-contenu-fhir---mise-à-jour-du-séjour/ig/StructureDefinition-tddui-careplan-projet-personnalise.xlsx
+++ b/422-contenu-fhir---mise-à-jour-du-séjour/ig/StructureDefinition-tddui-careplan-projet-personnalise.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-23T10:19:26+00:00</t>
+    <t>2026-02-23T14:19:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/422-contenu-fhir---mise-à-jour-du-séjour/ig/StructureDefinition-tddui-careplan-projet-personnalise.xlsx
+++ b/422-contenu-fhir---mise-à-jour-du-séjour/ig/StructureDefinition-tddui-careplan-projet-personnalise.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-23T14:19:51+00:00</t>
+    <t>2026-02-24T10:04:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -75,7 +75,7 @@
     <t>Jurisdiction</t>
   </si>
   <si>
-    <t>FRANCE</t>
+    <t>France</t>
   </si>
   <si>
     <t>Description</t>

--- a/422-contenu-fhir---mise-à-jour-du-séjour/ig/StructureDefinition-tddui-careplan-projet-personnalise.xlsx
+++ b/422-contenu-fhir---mise-à-jour-du-séjour/ig/StructureDefinition-tddui-careplan-projet-personnalise.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.2.0-ballot</t>
+    <t>2.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-24T10:04:30+00:00</t>
+    <t>2026-02-26T15:31:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1012,7 +1012,7 @@
     <t>TDDUI Status Author</t>
   </si>
   <si>
-    <t>Extension permettant de représenter la profession du professionnel.</t>
+    <t>Extension permettant de représenter l'auteur du statut.</t>
   </si>
   <si>
     <t>statutProjetPersonnalise.auteur</t>
